--- a/3th course/МИЭП/лаба 2 миэп.xlsx
+++ b/3th course/МИЭП/лаба 2 миэп.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/Универ/3th course/МИЭП/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB988CE0-4F8E-984C-894D-584A9EDAE37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ABE258-7479-3E4A-B1AD-FCD3FD87C63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{955C330A-0D08-FC45-92D3-890BE74BBC56}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16880" xr2:uid="{955C330A-0D08-FC45-92D3-890BE74BBC56}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
